--- a/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-identifier-type.xlsx
+++ b/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-identifier-type.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T15:07:43+00:00</t>
+    <t>2023-10-23T11:38:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-identifier-type.xlsx
+++ b/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-identifier-type.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-23T11:38:46+00:00</t>
+    <t>2023-11-06T10:27:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-identifier-type.xlsx
+++ b/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-identifier-type.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T10:27:25+00:00</t>
+    <t>2023-11-06T10:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-identifier-type.xlsx
+++ b/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-identifier-type.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T10:34:42+00:00</t>
+    <t>2023-11-06T13:10:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-identifier-type.xlsx
+++ b/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-identifier-type.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T13:10:33+00:00</t>
+    <t>2023-11-06T13:11:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-identifier-type.xlsx
+++ b/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-identifier-type.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T13:11:32+00:00</t>
+    <t>2023-11-06T13:13:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-identifier-type.xlsx
+++ b/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-identifier-type.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T13:13:14+00:00</t>
+    <t>2023-11-06T13:13:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-identifier-type.xlsx
+++ b/ig/nr-add-def-ins-collection/ValueSet-fr-core-practitioner-identifier-type.xlsx
@@ -8,7 +8,7 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include from identifierType" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from fr-v2-0203" r:id="rId5" sheetId="3"/>
+    <sheet name="Include from FR Core CodeSyst" r:id="rId5" sheetId="3"/>
     <sheet name="Include from TRE-G08-TypeIden" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
@@ -26,7 +26,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/ValueSet/fr-core-practitioner-identifier-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-practitioner-identifier-type</t>
   </si>
   <si>
     <t>Version</t>
@@ -38,13 +38,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>FRCoreValueSetPractionerIdentifierType</t>
+    <t>FRCoreValueSetPractitionerIdentifierType</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>FR Core ValueSet Practioner identifier type</t>
+    <t>FR Core ValueSet Practitioner identifier type</t>
   </si>
   <si>
     <t>Status</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T13:13:47+00:00</t>
+    <t>2023-11-08T15:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -77,7 +77,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for    a specific purpose (providers identification)</t>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose (providers identification)</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -134,7 +134,7 @@
     <t>Identifiant interne</t>
   </si>
   <si>
-    <t>http://interopsante.org/fhir/CodeSystem/fr-v2-0203</t>
+    <t>https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-0203</t>
   </si>
   <si>
     <t>1</t>
